--- a/reports/二级子公司D_利润表_2025-08.xlsx
+++ b/reports/二级子公司D_利润表_2025-08.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>93382795</v>
+        <v>94663420</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>91332141</v>
+        <v>90585790</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>654485358</v>
+        <v>654340802</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>314359</v>
+        <v>312374</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2256893</v>
+        <v>2255908</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>267697</v>
+        <v>268343</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1934336</v>
+        <v>1933901</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>225192</v>
+        <v>224182</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1612035</v>
+        <v>1611877</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>200403</v>
+        <v>202241</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1450789</v>
+        <v>1450972</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>112659</v>
+        <v>112558</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>805993</v>
+        <v>806237</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>89137</v>
+        <v>90130</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>644813</v>
+        <v>645068</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>92173348</v>
+        <v>93453592</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>90122694</v>
+        <v>89375962</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>5040683</v>
+        <v>5053700</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>36268395</v>
+        <v>36281785</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>392730</v>
+        <v>392112</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2821121</v>
+        <v>2821450</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>669549</v>
+        <v>670523</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>4835823</v>
+        <v>4835834</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>81044848</v>
+        <v>80293692</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>580335117</v>
+        <v>580191138</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1336170</v>
+        <v>1336426</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>9671878</v>
+        <v>9668415</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>450676</v>
+        <v>445319</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3223993</v>
+        <v>3222536</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2227808</v>
+        <v>2228172</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>16120269</v>
+        <v>16112628</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>562407</v>
+        <v>557958</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4029883</v>
+        <v>4028466</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2010625</v>
+        <v>2013234</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>14508561</v>
+        <v>14504571</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40029</v>
+        <v>40046</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>319984</v>
+        <v>320052</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1213784</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8706051</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>810566</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5805016</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>61316002</v>
+        <v>65636619</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>55084845</v>
+        <v>55009884</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>54082558</v>
+        <v>53999451</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>386880899</v>
+        <v>387043671</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1002287</v>
+        <v>1010433</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>7254092</v>
+        <v>7256218</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2015895</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>14509951</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>643502</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4642279</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>401376</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2900890</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>481062</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3480575</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>360721</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2610242</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>240683</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1740175</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>200920</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1450272</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>957681</v>
+        <v>951008</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6851046</v>
+        <v>6849536</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>723752</v>
+        <v>729073</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5239044</v>
+        <v>5238869</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>562824</v>
+        <v>562089</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4029910</v>
+        <v>4030679</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4240337</v>
+        <v>4278681</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>30629029</v>
+        <v>30638163</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>150285</v>
+        <v>169006</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1199950</v>
+        <v>1209526</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>320030</v>
+        <v>321792</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2560112</v>
+        <v>2560971</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>359252</v>
+        <v>321792</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2879877</v>
+        <v>2560971</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40153</v>
+        <v>40084</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>320012</v>
+        <v>320027</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161937</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1295861</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>351808</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2538681</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107488</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>863661</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>80528</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>647713</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>134204</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1079552</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>501517</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3625388</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>71778</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>575909</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>53962</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>432011</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90162</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>720148</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>63251</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>504176</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>45246</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>360155</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36216</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>288125</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27148</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>216080</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>30857346</v>
+        <v>29012136</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>35356413</v>
+        <v>32367675</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>201454</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1450921</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44860</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>359894</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>70198</v>
+        <v>69654</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>560022</v>
+        <v>559773</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>30787148</v>
+        <v>29143936</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2513797</v>
+        <v>2485433</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>20000388</v>
+        <v>19991889</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>28273351</v>
+        <v>26658503</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>28273351</v>
+        <v>26658503</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>28273351</v>
+        <v>26658503</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>28273351</v>
+        <v>26658503</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>28273351</v>
+        <v>26658503</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
